--- a/paper_draft/table/gherkin evaluator.xlsx
+++ b/paper_draft/table/gherkin evaluator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ker\Desktop\Document\paper\AgentOccam1\paper_draft\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66170FC5-C7B7-4A27-A776-1D1D8EE99F4B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3130581-EFD6-441D-A43B-EE1CB70AA341}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="9276" xr2:uid="{FD044680-57D5-43AE-BA20-D7D2A459AD94}"/>
   </bookViews>
@@ -27,48 +27,50 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>Evaluate the acceptance criterion and return JSON only.</t>
+    <t>System prompt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You are an expert at evaluating web automation test results against Gherkin acceptance criteria.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Criterion and evaluation evidence</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Acceptance Criterion: &lt;criterion&gt;
-Current Web Page:
-- URL: &lt;url&gt;
-- Title: &lt;title&gt;
-- Primary snapshot source: &lt;snapshot_source&gt;
-Accessibility tree text:
-&lt;accessibility_tree_text&gt;
-Fallback body text:
-&lt;body_text&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scoring standard:
-- 1.0: The criterion is satisfied by the page state.
-- 0.0: The criterion is not satisfied by the page state.
-- Only use one of these two scores.
-Return strict JSON with keys:
-{"score": &lt;0.0 or 1.0&gt;, "comment": "&lt;short reason in one sentence&gt;"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Criterion and page-state input</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Output constraint</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evaluation prompt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>System prompt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>You are an expert at evaluating web automation test results against Gherkin acceptance criteria.</t>
+Primary Evidence — Final Page State:
+- URL and title
+- Primary snapshot source
+- Accessibility tree or body text fallback
+Supporting Execution Evidence:
+- Compact action trace and operated elements
+- Typed values
+- Prior presence evidence for removal criteria</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evaluation rules</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Structured output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Judge whether the final page state satisfies the criterion.
+- 1.0: criterion satisfied
+- 0.0: criterion not satisfied
+- No partial score
+- Final absence alone is insufficient for removal criteria</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"score": &lt;0.0 or 1.0&gt;,
+ "comment": "&lt;short reason&gt;",
+ "needs_screenshot": &lt;true or false&gt;}
+Reevaluate with the final-page screenshot when requested.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -575,49 +577,49 @@
     <row r="2" spans="1:7" s="5" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10"/>
       <c r="B2" s="11" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
     </row>
-    <row r="3" spans="1:7" s="9" customFormat="1" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" s="9" customFormat="1" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="13" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" s="18"/>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="4" spans="1:7" s="7" customFormat="1" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" s="7" customFormat="1" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14"/>
       <c r="B4" s="15" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
     </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="3" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A5" s="16"/>
       <c r="B5" s="17" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -627,5 +629,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>